--- a/BWI/bestwine_output/bestwine_Slovenia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovenia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA99"/>
+  <dimension ref="A1:AA102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11481,6 +11481,357 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>Klara Todorović</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Consultant</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/klara-todorovi%c4%87-grilc-87547817b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>Rok Gabrovšek</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>Purchaser</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rok-gabrov%C5%A1ek-33898811b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>Leo Oberžan</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>Senior Buyer</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leo-ober%c5%bean-ll-m-7031a495/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovenia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovenia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA102"/>
+  <dimension ref="A1:AA105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11832,6 +11832,357 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>Klara Todorović</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Consultant</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/klara-todorovi%c4%87-grilc-87547817b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>Rok Gabrovšek</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>Purchaser</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rok-gabrov%C5%A1ek-33898811b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>Leo Oberžan</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>Senior Buyer</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leo-ober%c5%bean-ll-m-7031a495/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovenia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovenia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA105"/>
+  <dimension ref="A1:AA108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12183,6 +12183,357 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>Klara Todorović</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Consultant</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr"/>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/klara-todorovi%c4%87-grilc-87547817b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>Rok Gabrovšek</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>Purchaser</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rok-gabrov%C5%A1ek-33898811b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>Leo Oberžan</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>Senior Buyer</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leo-ober%c5%bean-ll-m-7031a495/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovenia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovenia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA108"/>
+  <dimension ref="A1:AA111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12534,6 +12534,357 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>Klara Todorović</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Consultant</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/klara-todorovi%c4%87-grilc-87547817b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>Rok Gabrovšek</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>Purchaser</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rok-gabrov%C5%A1ek-33898811b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Lidl Slovenija D.o.o. K.d.</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Komenda</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Kamnik</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>1 Pod lipami</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lidl.si</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>leo.oberzan@lidl.si</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>+386 1 888 92 72</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>1719947</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lidl-slovenija</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lidlslovenija/</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lidlslovenija</t>
+        </is>
+      </c>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/LidlSlovenijaSI</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>Leo Oberžan</t>
+        </is>
+      </c>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>Senior Buyer</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leo-ober%c5%bean-ll-m-7031a495/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovenia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovenia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA111"/>
+  <dimension ref="A1:AA112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12885,6 +12885,83 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Terlep Stanislav S.p.</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Terlep Stanislav S.p.</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>20050</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Ljubljana</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Ljubljana</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>240a Dolenjska cesta</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vina.si</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>stane.terlep@eunet.si</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="R112" s="2" t="inlineStr"/>
+      <c r="S112" s="2" t="inlineStr"/>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>Stanislav Terlep</t>
+        </is>
+      </c>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovenia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovenia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA112"/>
+  <dimension ref="A1:AA113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12962,6 +12962,71 @@
       <c r="Z112" s="2" t="inlineStr"/>
       <c r="AA112" s="2" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIC d.o.o. </t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>168333</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Dekani</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Dekani 2</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>https://ficdoo.si</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>fic.doo@siol.net</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>+386 5 659 25 18</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr"/>
+      <c r="R113" s="2" t="inlineStr"/>
+      <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr"/>
+      <c r="X113" s="2" t="inlineStr"/>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
